--- a/output/tables/B25_Table1_publication_format.xlsx
+++ b/output/tables/B25_Table1_publication_format.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10817"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizabeth/Documents/GitHub/ice-sheet-sej-2025/output/tables/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABBEB09-2B6D-E840-9F5A-FFE00EFAC032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="25440" windowHeight="18640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -607,8 +601,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -662,8 +656,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -677,39 +674,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -747,7 +724,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -781,7 +758,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -816,10 +792,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -992,792 +967,750 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.6640625" customWidth="1"/>
-    <col min="2" max="5" width="14.6640625" customWidth="1"/>
-    <col min="6" max="6" width="3.83203125" customWidth="1"/>
-    <col min="7" max="10" width="14.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.83203125" customWidth="1"/>
-    <col min="12" max="15" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="13" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="8" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="8" t="s">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="9"/>
-      <c r="B4" s="1" t="s">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="I4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="1" t="s">
+      <c r="J4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="K4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="L4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="M4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
+    <row r="5" spans="1:13">
+      <c r="A5" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:13">
+      <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4" t="s">
+      <c r="J6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="L6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="M6" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:13">
+      <c r="A7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4" t="s">
+      <c r="J7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="K7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="L7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="M7" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:13">
+      <c r="A8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4" t="s">
+      <c r="J8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="K8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="L8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="M8" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:13">
+      <c r="A9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="G9" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4" t="s">
+      <c r="J9" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="K9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="L9" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="M9" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:13">
+      <c r="A10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="G10" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="I10" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4" t="s">
+      <c r="J10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="K10" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="L10" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="M10" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
+    <row r="11" spans="1:13">
+      <c r="A11" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:13">
+      <c r="A12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="G12" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="I12" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4" t="s">
+      <c r="J12" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="K12" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N12" s="4" t="s">
+      <c r="L12" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="O12" s="4" t="s">
+      <c r="M12" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:13">
+      <c r="A13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="G13" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="H13" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="I13" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4" t="s">
+      <c r="J13" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="K13" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="N13" s="4" t="s">
+      <c r="L13" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="M13" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:13">
+      <c r="A14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="G14" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="H14" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="I14" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4" t="s">
+      <c r="J14" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="M14" s="4" t="s">
+      <c r="K14" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="N14" s="4" t="s">
+      <c r="L14" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="O14" s="4" t="s">
+      <c r="M14" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:13">
+      <c r="A15" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4" t="s">
+      <c r="F15" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="G15" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="H15" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="I15" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4" t="s">
+      <c r="J15" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="K15" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="L15" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="O15" s="4" t="s">
+      <c r="M15" s="5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:13">
+      <c r="A16" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4" t="s">
+      <c r="F16" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="G16" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="H16" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="I16" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4" t="s">
+      <c r="J16" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="M16" s="4" t="s">
+      <c r="K16" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="N16" s="4" t="s">
+      <c r="L16" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="O16" s="4" t="s">
+      <c r="M16" s="5" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
+    <row r="17" spans="1:13">
+      <c r="A17" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:13">
+      <c r="A18" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4" t="s">
+      <c r="F18" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="G18" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="H18" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="I18" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4" t="s">
+      <c r="J18" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="M18" s="4" t="s">
+      <c r="K18" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="N18" s="4" t="s">
+      <c r="L18" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="O18" s="4" t="s">
+      <c r="M18" s="5" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:13">
+      <c r="A19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4" t="s">
+      <c r="F19" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="G19" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="H19" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="I19" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4" t="s">
+      <c r="J19" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="M19" s="4" t="s">
+      <c r="K19" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="N19" s="4" t="s">
+      <c r="L19" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="O19" s="4" t="s">
+      <c r="M19" s="5" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:13">
+      <c r="A20" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4" t="s">
+      <c r="F20" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="G20" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="H20" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="I20" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4" t="s">
+      <c r="J20" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="M20" s="4" t="s">
+      <c r="K20" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="N20" s="4" t="s">
+      <c r="L20" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="M20" s="5" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:13">
+      <c r="A21" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4" t="s">
+      <c r="F21" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="G21" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="H21" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="I21" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4" t="s">
+      <c r="J21" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="M21" s="4" t="s">
+      <c r="K21" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="N21" s="4" t="s">
+      <c r="L21" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="O21" s="4" t="s">
+      <c r="M21" s="5" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:13">
+      <c r="A22" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4" t="s">
+      <c r="F22" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="G22" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="H22" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="I22" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4" t="s">
+      <c r="J22" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="M22" s="4" t="s">
+      <c r="K22" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="N22" s="4" t="s">
+      <c r="L22" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="O22" s="4" t="s">
+      <c r="M22" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
+    <row r="23" spans="1:13">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:M1"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="55" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>
--- a/output/tables/B25_Table1_publication_format.xlsx
+++ b/output/tables/B25_Table1_publication_format.xlsx
@@ -1,20 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizabeth/Documents/GitHub/ice-sheet-sej-2025/output/tables/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88511F2-83A4-5A4E-9F84-C2CF8FE925D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="6520" yWindow="760" windowWidth="29880" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="235">
   <si>
     <t>Table 1. Projected sea-level rise contributions from each ice sheet and combined</t>
   </si>
@@ -596,13 +616,136 @@
   </si>
   <si>
     <t>1360–7200</t>
+  </si>
+  <si>
+    <t>−2–15</t>
+  </si>
+  <si>
+    <t>1–10</t>
+  </si>
+  <si>
+    <t>−2–56</t>
+  </si>
+  <si>
+    <t>1–30</t>
+  </si>
+  <si>
+    <t>−1–42</t>
+  </si>
+  <si>
+    <t>3–27</t>
+  </si>
+  <si>
+    <t>−5–52</t>
+  </si>
+  <si>
+    <t>−1–27</t>
+  </si>
+  <si>
+    <t>7–16</t>
+  </si>
+  <si>
+    <t>4–21</t>
+  </si>
+  <si>
+    <t>−1–51</t>
+  </si>
+  <si>
+    <t>3–31</t>
+  </si>
+  <si>
+    <t>AIS (IPCC AR6, SSP1-2.6, MEDIUM CONF.)</t>
+  </si>
+  <si>
+    <t>AIS (IPCC AR6, SSP1-2.6, LOW CONF.)</t>
+  </si>
+  <si>
+    <t>AIS (IPCC AR6, SSP1-3.7, MEDIUM CONF.)</t>
+  </si>
+  <si>
+    <t>GrIS (IPCC AR6, SSP1-2.6, MEDIUM CONF.)</t>
+  </si>
+  <si>
+    <t>GrIS (IPCC AR6, SSP1-2.6, LOW CONF.)</t>
+  </si>
+  <si>
+    <t>GrIS (IPCC AR6, SSP1-3.7, MEDIUM CONF.)</t>
+  </si>
+  <si>
+    <t>1–18</t>
+  </si>
+  <si>
+    <t>4–13</t>
+  </si>
+  <si>
+    <t>9–26</t>
+  </si>
+  <si>
+    <t>11–20</t>
+  </si>
+  <si>
+    <t>GrIS (2100 FACTS, MEDIUM CONF.)</t>
+  </si>
+  <si>
+    <t>AIS (2100 FACTS, MEDIUM CONF.)</t>
+  </si>
+  <si>
+    <t>−1–43</t>
+  </si>
+  <si>
+    <t>3–28</t>
+  </si>
+  <si>
+    <t>0–?</t>
+  </si>
+  <si>
+    <t>4–35</t>
+  </si>
+  <si>
+    <t>GRIS (SSP1-2.6)</t>
+  </si>
+  <si>
+    <t>11–25</t>
+  </si>
+  <si>
+    <t>AIS (SSP1-2.6)</t>
+  </si>
+  <si>
+    <t>−14–78</t>
+  </si>
+  <si>
+    <t>AIS (MICI, SSP1-2.6)</t>
+  </si>
+  <si>
+    <t>71–135</t>
+  </si>
+  <si>
+    <t>GrIS (ISMIP6; SSP1-2.6)</t>
+  </si>
+  <si>
+    <t>AIS (ISMIP6; SSP1-2.6)</t>
+  </si>
+  <si>
+    <t>−1–19</t>
+  </si>
+  <si>
+    <t>3–14</t>
+  </si>
+  <si>
+    <t>AIS (LARMIP2; SSP1-2.6)</t>
+  </si>
+  <si>
+    <t>3–41</t>
+  </si>
+  <si>
+    <t>6–27</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -622,6 +765,142 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF92D050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF2F92"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF7E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF8AD8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="6" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF40FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF40FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF008F00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF008F00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFD883FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFD883FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="7"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -656,37 +935,154 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFD883FF"/>
+      <color rgb="FF008F00"/>
+      <color rgb="FFFF40FF"/>
+      <color rgb="FFFF8AD8"/>
+      <color rgb="FFFF7E79"/>
+      <color rgb="FFFF2F92"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -724,7 +1120,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -758,6 +1154,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -792,9 +1189,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -967,740 +1365,740 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="13" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" customWidth="1"/>
+    <col min="2" max="13" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2" t="s">
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2" t="s">
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="21"/>
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
         <v>2100</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="M6" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="L7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="M7" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="L8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="M8" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="5" t="s">
+      <c r="L9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="M9" s="5" t="s">
+      <c r="M9" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="L10" s="5" t="s">
+      <c r="L10" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="M10" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
         <v>2200</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="L12" s="5" t="s">
+      <c r="L12" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="M12" s="5" t="s">
+      <c r="M12" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="L13" s="5" t="s">
+      <c r="L13" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="M13" s="5" t="s">
+      <c r="M13" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K14" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="L14" s="5" t="s">
+      <c r="L14" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="M14" s="5" t="s">
+      <c r="M14" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="K15" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="L15" s="5" t="s">
+      <c r="L15" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="M15" s="5" t="s">
+      <c r="M15" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="L16" s="5" t="s">
+      <c r="L16" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="M16" s="5" t="s">
+      <c r="M16" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
         <v>2300</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="K18" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="L18" s="5" t="s">
+      <c r="L18" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="M18" s="5" t="s">
+      <c r="M18" s="4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="K19" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="L19" s="5" t="s">
+      <c r="L19" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="M19" s="5" t="s">
+      <c r="M19" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="J20" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="K20" s="5" t="s">
+      <c r="K20" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="L20" s="5" t="s">
+      <c r="L20" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="M20" s="5" t="s">
+      <c r="M20" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K21" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="L21" s="5" t="s">
+      <c r="L21" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="M21" s="5" t="s">
+      <c r="M21" s="4" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="K22" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="L22" s="5" t="s">
+      <c r="L22" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="M22" s="5" t="s">
+      <c r="M22" s="4" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1713,4 +2111,1111 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1EE492C-228E-5648-865A-C7CC91E20E1E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="38.83203125" customWidth="1"/>
+    <col min="2" max="13" width="14.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="21"/>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="13">
+        <v>11</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+    </row>
+    <row r="10" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="B10" s="27"/>
+      <c r="C10" s="28">
+        <v>11</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="28">
+        <v>12</v>
+      </c>
+      <c r="L10" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="M10" s="28" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="15">
+        <v>10</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" spans="1:13" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="B12" s="36"/>
+      <c r="C12" s="37">
+        <v>9</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>230</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+    </row>
+    <row r="13" spans="1:13" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="B13" s="40"/>
+      <c r="C13" s="41">
+        <v>13</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="17">
+        <v>11</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" s="16"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="11">
+        <v>6</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+    </row>
+    <row r="18" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="B18" s="23"/>
+      <c r="C18" s="24">
+        <v>8</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="24">
+        <v>15</v>
+      </c>
+      <c r="L18" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="M18" s="24" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="10">
+        <v>9</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+    </row>
+    <row r="20" spans="1:13" s="34" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="B20" s="32"/>
+      <c r="C20" s="33">
+        <v>6</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="18">
+        <v>11</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A35" s="26"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+    </row>
+    <row r="36" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="M36" s="9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="53" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>